--- a/Project_CNN/DenseNet/Resultados/Experimento 2 - DenseNet/training_metrics.xlsx
+++ b/Project_CNN/DenseNet/Resultados/Experimento 2 - DenseNet/training_metrics.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marci_wawp\Desktop\Arquivos\Mestrado\Projeto-Classificadores\Project_CNN\DenseNet\Resultados\Experimento 2 - DenseNet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7D8AA5F-933A-435D-90D6-2CDCE4F93068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984B377C-379E-4FF7-B0D6-445A0A8B59CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="999999"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -114,6 +114,31 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2640" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t>DenseNet - Accuracy Curves</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -127,7 +152,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="2640" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -146,8 +171,8 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -175,7 +200,7 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:val>
+          <c:yVal>
             <c:numRef>
               <c:f>Worksheet!$B$2:$B$100</c:f>
               <c:numCache>
@@ -480,8 +505,8 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
+          </c:yVal>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-2128-4D08-AFE0-321B312E23F4}"/>
@@ -514,7 +539,7 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:val>
+          <c:yVal>
             <c:numRef>
               <c:f>Worksheet!$E$2:$E$100</c:f>
               <c:numCache>
@@ -819,8 +844,8 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
+          </c:yVal>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-2128-4D08-AFE0-321B312E23F4}"/>
@@ -835,17 +860,73 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:smooth val="0"/>
         <c:axId val="1913391679"/>
         <c:axId val="1913375359"/>
-      </c:lineChart>
-      <c:catAx>
+      </c:scatterChart>
+      <c:valAx>
         <c:axId val="1913391679"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="99"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="2200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR"/>
+                  <a:t>Epochs</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="2200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -867,7 +948,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -884,15 +965,15 @@
         </c:txPr>
         <c:crossAx val="1913375359"/>
         <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
+        <c:crossBetween val="midCat"/>
+        <c:minorUnit val="1"/>
+      </c:valAx>
       <c:valAx>
         <c:axId val="1913375359"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="1"/>
+          <c:min val="0.2"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -910,6 +991,61 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="2200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR"/>
+                  <a:t>Accuracy (%)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="2200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -926,7 +1062,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -943,7 +1079,8 @@
         </c:txPr>
         <c:crossAx val="1913391679"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
+        <c:minorUnit val="1.0000000000000002E-2"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -968,7 +1105,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="2200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -1015,7 +1152,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr sz="2200" baseline="0"/>
       </a:pPr>
       <a:endParaRPr lang="pt-BR"/>
     </a:p>
@@ -1043,6 +1180,35 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2640" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t>DenseNet</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="pt-BR" baseline="0"/>
+              <a:t> - Loss Curves</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1056,7 +1222,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="2640" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -1075,8 +1241,8 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -1104,7 +1270,7 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:val>
+          <c:yVal>
             <c:numRef>
               <c:f>Worksheet!$C$2:$C$100</c:f>
               <c:numCache>
@@ -1409,8 +1575,8 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
+          </c:yVal>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-DE8E-4E6F-8C88-698971F6AAE4}"/>
@@ -1443,7 +1609,7 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:val>
+          <c:yVal>
             <c:numRef>
               <c:f>Worksheet!$F$2:$F$100</c:f>
               <c:numCache>
@@ -1748,8 +1914,8 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
+          </c:yVal>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-DE8E-4E6F-8C88-698971F6AAE4}"/>
@@ -1764,17 +1930,73 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:smooth val="0"/>
         <c:axId val="1913393599"/>
         <c:axId val="1913394079"/>
-      </c:lineChart>
-      <c:catAx>
+      </c:scatterChart>
+      <c:valAx>
         <c:axId val="1913393599"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="99"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="2200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR"/>
+                  <a:t>Epochs</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="2200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1796,7 +2018,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1813,15 +2035,13 @@
         </c:txPr>
         <c:crossAx val="1913394079"/>
         <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
       <c:valAx>
         <c:axId val="1913394079"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="4.5"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1839,6 +2059,61 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="2200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR"/>
+                  <a:t>Loss</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="2200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1855,7 +2130,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1872,7 +2147,7 @@
         </c:txPr>
         <c:crossAx val="1913393599"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -1897,7 +2172,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="2200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -1944,7 +2219,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr sz="2200" baseline="0"/>
       </a:pPr>
       <a:endParaRPr lang="pt-BR"/>
     </a:p>
@@ -3074,15 +3349,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>4762</xdr:rowOff>
+      <xdr:colOff>2380</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>107156</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:colOff>272142</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3110,15 +3385,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>42861</xdr:rowOff>
+      <xdr:colOff>4481</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>81521</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>9524</xdr:rowOff>
+      <xdr:colOff>272142</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>59531</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3433,7 +3708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F100"/>
+  <dimension ref="A1:F102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17" customWidth="1"/>
@@ -5442,6 +5717,24 @@
         <v>0.30480843782424999</v>
       </c>
     </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B102">
+        <f>AVERAGE(B86:B100)</f>
+        <v>0.99183070659637529</v>
+      </c>
+      <c r="C102">
+        <f>AVERAGE(C86:C100)</f>
+        <v>2.8602144991358141E-2</v>
+      </c>
+      <c r="E102">
+        <f>AVERAGE(E86:E100)</f>
+        <v>0.91825082302093586</v>
+      </c>
+      <c r="F102">
+        <f>AVERAGE(F86:F100)</f>
+        <v>0.30510261654853932</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Project_CNN/DenseNet/Resultados/Experimento 2 - DenseNet/training_metrics.xlsx
+++ b/Project_CNN/DenseNet/Resultados/Experimento 2 - DenseNet/training_metrics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marci_wawp\Desktop\Arquivos\Mestrado\Projeto-Classificadores\Project_CNN\DenseNet\Resultados\Experimento 2 - DenseNet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984B377C-379E-4FF7-B0D6-445A0A8B59CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF382727-BB10-420D-9D42-EDEFB61C5F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="2520" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>

--- a/Project_CNN/DenseNet/Resultados/Experimento 2 - DenseNet/training_metrics.xlsx
+++ b/Project_CNN/DenseNet/Resultados/Experimento 2 - DenseNet/training_metrics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marci_wawp\Desktop\Arquivos\Mestrado\Projeto-Classificadores\Project_CNN\DenseNet\Resultados\Experimento 2 - DenseNet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF382727-BB10-420D-9D42-EDEFB61C5F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B807E70F-3580-41F7-8D97-34CBE32C7461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="2520" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -120,7 +120,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="2640" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="2400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -152,7 +152,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="2640" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="2400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -867,7 +867,7 @@
         <c:axId val="1913391679"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="99"/>
+          <c:max val="100"/>
           <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -879,7 +879,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="2200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -911,7 +911,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="2200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -948,7 +948,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="2200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -998,7 +998,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="2200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -1030,7 +1030,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="2200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -1062,7 +1062,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="2200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1105,7 +1105,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="2200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -1152,7 +1152,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr sz="2200" baseline="0"/>
+        <a:defRPr sz="2000" baseline="0"/>
       </a:pPr>
       <a:endParaRPr lang="pt-BR"/>
     </a:p>
@@ -1186,7 +1186,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="2640" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="2400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1200,11 +1200,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="pt-BR"/>
-              <a:t>DenseNet</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="pt-BR" baseline="0"/>
-              <a:t> - Loss Curves</a:t>
+              <a:t>DenseNet - Loss Curves</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1222,7 +1218,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="2640" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="2400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -1937,7 +1933,7 @@
         <c:axId val="1913393599"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="99"/>
+          <c:max val="100"/>
           <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -1949,7 +1945,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="2200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -1981,7 +1977,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="2200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -2018,7 +2014,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="2200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -2042,6 +2038,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="4.5"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -2066,7 +2063,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="2200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -2098,7 +2095,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="2200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -2130,7 +2127,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="2200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -2172,7 +2169,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="2200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -2219,7 +2216,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr sz="2200" baseline="0"/>
+        <a:defRPr sz="2000" baseline="0"/>
       </a:pPr>
       <a:endParaRPr lang="pt-BR"/>
     </a:p>
@@ -3350,14 +3347,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>2380</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>107156</xdr:rowOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>272142</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>9524</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3386,14 +3383,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>4481</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>81521</xdr:rowOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>272142</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>59531</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
